--- a/INSTANCES/instances_literature_xlsx/A_MTN_3/354FL_8A_17.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_3/354FL_8A_17.xlsx
@@ -10569,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -10586,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -10603,7 +10603,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>

--- a/INSTANCES/instances_literature_xlsx/A_MTN_3/354FL_8A_17.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_3/354FL_8A_17.xlsx
@@ -9848,16 +9848,16 @@
         <v>480</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>78.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12.0</v>
       </c>
       <c r="F2">
         <v>7</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>479</v>
@@ -9925,7 +9925,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -9936,13 +9936,13 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -9971,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -9988,22 +9988,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -10023,7 +10023,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -10073,10 +10073,10 @@
         <v>5700</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>75.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10090,10 +10090,10 @@
         <v>4955</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>65.0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10107,10 +10107,10 @@
         <v>3760</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>49.0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
